--- a/models/vggt/vggt_results.xlsx
+++ b/models/vggt/vggt_results.xlsx
@@ -6410,7 +6410,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>outputs/mural_king_scen_3/reconstruction.glb</t>
+          <t>outputs/custom_mural_king_scen_3/reconstruction.glb</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -6432,76 +6432,76 @@
         <v>3</v>
       </c>
       <c r="M40">
-        <v>4.049627930999122</v>
+        <v>3.7827130609998676</v>
       </c>
       <c r="N40">
-        <v>19.83704132800085</v>
+        <v>17.438522168999953</v>
       </c>
       <c r="O40">
-        <v>3.568447214000116</v>
+        <v>3.1327943030000824</v>
       </c>
       <c r="P40">
-        <v>10.812510320000001</v>
+        <v>9.336315648999971</v>
       </c>
       <c r="Q40">
-        <v>34.95262277599977</v>
+        <v>30.824766395000097</v>
       </c>
       <c r="R40">
-        <v>2.594925511999463</v>
+        <v>2.200725779000095</v>
       </c>
       <c r="S40">
-        <v>2.0907508799991774</v>
+        <v>1.896028729000136</v>
       </c>
       <c r="T40">
-        <v>2.671209780999561</v>
+        <v>2.2459688019998794</v>
       </c>
       <c r="U40">
-        <v>0.6872621189995698</v>
+        <v>0.7135851940001885</v>
       </c>
       <c r="V40">
-        <v>0.6822326170004089</v>
+        <v>0.4905782190003265</v>
       </c>
       <c r="W40">
-        <v>1.2296445169995422</v>
+        <v>1.0737326530002065</v>
       </c>
       <c r="X40">
-        <v>0.054548705000343034</v>
+        <v>0.04477275399995051</v>
       </c>
       <c r="Y40">
-        <v>0.0467414809991169</v>
+        <v>0.038257295999756025</v>
       </c>
       <c r="Z40">
-        <v>0.11021760699986771</v>
+        <v>0.09973776000015278</v>
       </c>
       <c r="AA40">
-        <v>0.15996927000014693</v>
+        <v>0.14383747600004426</v>
       </c>
       <c r="AB40">
-        <v>0.15447452000080375</v>
+        <v>0.13465033200009202</v>
       </c>
       <c r="AC40">
-        <v>0.21714035900004092</v>
+        <v>0.14677485799984424</v>
       </c>
       <c r="AD40">
-        <v>3.4838336369994067</v>
+        <v>2.8803785439999956</v>
       </c>
       <c r="AE40">
-        <v>3.648160597998867</v>
+        <v>3.2166919649998817</v>
       </c>
       <c r="AF40">
-        <v>10327.65625</v>
+        <v>10334.328125</v>
       </c>
       <c r="AG40">
-        <v>1986.90234375</v>
+        <v>2004.1953125</v>
       </c>
       <c r="AH40">
-        <v>1686.875</v>
+        <v>1695.0625</v>
       </c>
       <c r="AI40">
-        <v>1994.42578125</v>
+        <v>2011.77734375</v>
       </c>
       <c r="AJ40">
-        <v>10327.65625</v>
+        <v>10333.26953125</v>
       </c>
       <c r="AK40">
         <v>4798.52783203125</v>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>outputs/synagogue_scen_2/reconstruction.glb</t>
+          <t>outputs/custom_synagogue_scen_2/reconstruction.glb</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -11997,76 +11997,76 @@
         <v>3</v>
       </c>
       <c r="M75">
-        <v>4.206047657000454</v>
+        <v>3.9077557929999784</v>
       </c>
       <c r="N75">
-        <v>19.83248505099982</v>
+        <v>17.319810020999967</v>
       </c>
       <c r="O75">
-        <v>1.9799743599996873</v>
+        <v>1.58654995400002</v>
       </c>
       <c r="P75">
-        <v>5.886975016000179</v>
+        <v>5.081649946000198</v>
       </c>
       <c r="Q75">
-        <v>30.18098534099954</v>
+        <v>26.56224979600006</v>
       </c>
       <c r="R75">
-        <v>1.3078438390002702</v>
+        <v>1.1542865450001045</v>
       </c>
       <c r="S75">
-        <v>1.0754642120000426</v>
+        <v>0.9546142080002937</v>
       </c>
       <c r="T75">
-        <v>1.3766786769992905</v>
+        <v>1.1555849840001429</v>
       </c>
       <c r="U75">
-        <v>0.5009093979997488</v>
+        <v>0.33644842200010316</v>
       </c>
       <c r="V75">
-        <v>0.3022157400000651</v>
+        <v>0.29522784600021623</v>
       </c>
       <c r="W75">
-        <v>0.8000040209999497</v>
+        <v>0.768623246000061</v>
       </c>
       <c r="X75">
-        <v>0.052163829000164696</v>
+        <v>0.023531820000243897</v>
       </c>
       <c r="Y75">
-        <v>0.02497786499952781</v>
+        <v>0.022368996999830415</v>
       </c>
       <c r="Z75">
-        <v>0.11020431500037375</v>
+        <v>0.045829979999780335</v>
       </c>
       <c r="AA75">
-        <v>0.07702487400001701</v>
+        <v>0.07283531399980347</v>
       </c>
       <c r="AB75">
-        <v>0.0728769530005593</v>
+        <v>0.07169309599976259</v>
       </c>
       <c r="AC75">
-        <v>0.08316216000002896</v>
+        <v>0.07764049400020667</v>
       </c>
       <c r="AD75">
-        <v>1.7935079819999373</v>
+        <v>1.546279799000331</v>
       </c>
       <c r="AE75">
-        <v>2.011256527000114</v>
+        <v>1.8471103329998186</v>
       </c>
       <c r="AF75">
-        <v>10327.2109375</v>
+        <v>10334.9296875</v>
       </c>
       <c r="AG75">
-        <v>1970.875</v>
+        <v>1980.171875</v>
       </c>
       <c r="AH75">
-        <v>1629.30859375</v>
+        <v>1638.61328125</v>
       </c>
       <c r="AI75">
-        <v>1980.11328125</v>
+        <v>1989.515625</v>
       </c>
       <c r="AJ75">
-        <v>10327.2109375</v>
+        <v>10333.625</v>
       </c>
       <c r="AK75">
         <v>4798.52783203125</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>outputs/tennis_table_scen_3/reconstruction.glb</t>
+          <t>outputs/custom_tennis_table_scen_3/reconstruction.glb</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -12792,76 +12792,76 @@
         <v>3</v>
       </c>
       <c r="M80">
-        <v>4.080199928000184</v>
+        <v>3.5676151449997633</v>
       </c>
       <c r="N80">
-        <v>19.836511888000132</v>
+        <v>17.30695168200009</v>
       </c>
       <c r="O80">
-        <v>3.6518481220000467</v>
+        <v>3.057930276999741</v>
       </c>
       <c r="P80">
-        <v>11.145773394000571</v>
+        <v>9.58461885099996</v>
       </c>
       <c r="Q80">
-        <v>35.31652098199993</v>
+        <v>30.7224776879998</v>
       </c>
       <c r="R80">
-        <v>2.7058240480000677</v>
+        <v>2.208074852000209</v>
       </c>
       <c r="S80">
-        <v>2.1329446460003965</v>
+        <v>2.0334740280000005</v>
       </c>
       <c r="T80">
-        <v>2.8444968600006177</v>
+        <v>2.2287902489997578</v>
       </c>
       <c r="U80">
-        <v>0.7581648529994709</v>
+        <v>0.6669400360001418</v>
       </c>
       <c r="V80">
-        <v>0.639344064999932</v>
+        <v>0.5121837249998862</v>
       </c>
       <c r="W80">
-        <v>1.1745750850004697</v>
+        <v>1.1493468550002035</v>
       </c>
       <c r="X80">
-        <v>0.058149243999650935</v>
+        <v>0.04412555499993687</v>
       </c>
       <c r="Y80">
-        <v>0.05534724300014204</v>
+        <v>0.039332020999609085</v>
       </c>
       <c r="Z80">
-        <v>0.12425867799993284</v>
+        <v>0.08916055100007725</v>
       </c>
       <c r="AA80">
-        <v>0.15988742200079287</v>
+        <v>0.14166901699991286</v>
       </c>
       <c r="AB80">
-        <v>0.15845751599954383</v>
+        <v>0.13838934799969138</v>
       </c>
       <c r="AC80">
-        <v>0.2196271679995334</v>
+        <v>0.1515617810000549</v>
       </c>
       <c r="AD80">
-        <v>3.5594197660002465</v>
+        <v>2.92237920100024</v>
       </c>
       <c r="AE80">
-        <v>3.8211407339995276</v>
+        <v>3.424120740000035</v>
       </c>
       <c r="AF80">
-        <v>10327.23046875</v>
+        <v>10334.5859375</v>
       </c>
       <c r="AG80">
-        <v>1994.62890625</v>
+        <v>2005.34375</v>
       </c>
       <c r="AH80">
-        <v>1686.51171875</v>
+        <v>1695.2890625</v>
       </c>
       <c r="AI80">
-        <v>2013.3203125</v>
+        <v>2012.87890625</v>
       </c>
       <c r="AJ80">
-        <v>10327.23046875</v>
+        <v>10333.30859375</v>
       </c>
       <c r="AK80">
         <v>4798.52783203125</v>
@@ -15177,76 +15177,76 @@
         <v>3</v>
       </c>
       <c r="M95">
-        <v>4.0004823770004805</v>
+        <v>6.355123439999943</v>
       </c>
       <c r="N95">
-        <v>20.56769662700026</v>
+        <v>29.527489297000102</v>
       </c>
       <c r="O95">
-        <v>1.2335288760004914</v>
+        <v>1.0496068570000716</v>
       </c>
       <c r="P95">
-        <v>3.817830681000487</v>
+        <v>4.364976634000186</v>
       </c>
       <c r="Q95">
-        <v>28.6502042660004</v>
+        <v>40.4937164009998</v>
       </c>
       <c r="R95">
-        <v>0.7445004020000852</v>
+        <v>0.6386885040001289</v>
       </c>
       <c r="S95">
-        <v>0.4821823719994427</v>
+        <v>0.61447330399983</v>
       </c>
       <c r="T95">
-        <v>0.8139052559999982</v>
+        <v>0.6448907740000323</v>
       </c>
       <c r="U95">
-        <v>0.37045045899958495</v>
+        <v>0.31655893400011337</v>
       </c>
       <c r="V95">
-        <v>0.30861644499964314</v>
+        <v>0.3083011210001132</v>
       </c>
       <c r="W95">
-        <v>0.6858818979999342</v>
+        <v>1.4240024959999573</v>
       </c>
       <c r="X95">
-        <v>0.024357030999453855</v>
+        <v>0.0214336500000627</v>
       </c>
       <c r="Y95">
-        <v>0.018257450999954017</v>
+        <v>0.020963550000033138</v>
       </c>
       <c r="Z95">
-        <v>0.04753156900005706</v>
+        <v>0.05657598900006633</v>
       </c>
       <c r="AA95">
-        <v>0.07052249000025768</v>
+        <v>0.06761589899997489</v>
       </c>
       <c r="AB95">
-        <v>0.0702024430001984</v>
+        <v>0.0667658190000111</v>
       </c>
       <c r="AC95">
-        <v>0.08624562499971944</v>
+        <v>0.08636311300006128</v>
       </c>
       <c r="AD95">
-        <v>1.2041529259995514</v>
+        <v>1.0122489479999786</v>
       </c>
       <c r="AE95">
-        <v>1.286158740999781</v>
+        <v>2.206190276000143</v>
       </c>
       <c r="AF95">
-        <v>10268.37890625</v>
+        <v>10332.56640625</v>
       </c>
       <c r="AG95">
-        <v>1783.1796875</v>
+        <v>1789.0078125</v>
       </c>
       <c r="AH95">
-        <v>1620.3046875</v>
+        <v>1626.8203125</v>
       </c>
       <c r="AI95">
-        <v>1787.22265625</v>
+        <v>1796.3671875</v>
       </c>
       <c r="AJ95">
-        <v>10327.50390625</v>
+        <v>10330.95703125</v>
       </c>
       <c r="AK95">
         <v>4798.52783203125</v>
@@ -19443,7 +19443,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/nerf_llff_data/fern/images/scen_1/IMG_4026.JPG</t>
+          <t>/home/kamil/dataset/nerf_llff_data/fern/images/scen_1/IMG_4029.JPG</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -19470,76 +19470,76 @@
         <v>3</v>
       </c>
       <c r="M122">
-        <v>6.017645576000007</v>
+        <v>5.004816653000034</v>
       </c>
       <c r="N122">
-        <v>22.750858658000027</v>
+        <v>20.788060594999934</v>
       </c>
       <c r="O122">
-        <v>0.510129027000005</v>
+        <v>0.5602415260000271</v>
       </c>
       <c r="P122">
-        <v>2.311321018000001</v>
+        <v>2.4362874490000195</v>
       </c>
       <c r="Q122">
-        <v>31.35535857299996</v>
+        <v>28.520556282000143</v>
       </c>
       <c r="R122">
-        <v>0.15803509200003418</v>
+        <v>0.14500359399994522</v>
       </c>
       <c r="S122">
-        <v>0.11907342599999993</v>
+        <v>0.12731721699992704</v>
       </c>
       <c r="T122">
-        <v>0.18747748799995634</v>
+        <v>0.14810585999998693</v>
       </c>
       <c r="U122">
-        <v>0.27211605299999064</v>
+        <v>0.3657031380000717</v>
       </c>
       <c r="V122">
-        <v>0.23807987800000774</v>
+        <v>0.25727351399996223</v>
       </c>
       <c r="W122">
-        <v>1.0815381880000245</v>
+        <v>1.139337926000053</v>
       </c>
       <c r="X122">
-        <v>0.014657782999961455</v>
+        <v>0.014654044999815596</v>
       </c>
       <c r="Y122">
-        <v>0.01402968200000032</v>
+        <v>0.012213914999847475</v>
       </c>
       <c r="Z122">
-        <v>0.044484061999980895</v>
+        <v>0.03962344599995049</v>
       </c>
       <c r="AA122">
-        <v>0.036388001999966946</v>
+        <v>0.036942236999948364</v>
       </c>
       <c r="AB122">
-        <v>0.036214778999976716</v>
+        <v>0.03405891500005964</v>
       </c>
       <c r="AC122">
-        <v>0.04529757700004211</v>
+        <v>0.0452711249999993</v>
       </c>
       <c r="AD122">
-        <v>0.44741061100000934</v>
+        <v>0.454484445999924</v>
       </c>
       <c r="AE122">
-        <v>1.2907030189999773</v>
+        <v>1.3521266019999985</v>
       </c>
       <c r="AF122">
-        <v>10324.703125</v>
+        <v>10331.76171875</v>
       </c>
       <c r="AG122">
-        <v>1744.96875</v>
+        <v>1753.9140625</v>
       </c>
       <c r="AH122">
-        <v>1666.09375</v>
+        <v>1675.02734375</v>
       </c>
       <c r="AI122">
-        <v>1745.109375</v>
+        <v>1758.6015625</v>
       </c>
       <c r="AJ122">
-        <v>10324.703125</v>
+        <v>10330.68359375</v>
       </c>
       <c r="AK122">
         <v>4798.52783203125</v>
@@ -31480,28 +31480,28 @@
         <v>1</v>
       </c>
       <c r="G116">
-        <v>2.0907508799991774</v>
+        <v>1.896028729000136</v>
       </c>
       <c r="H116">
-        <v>1.2296445169995422</v>
+        <v>1.0737326530002065</v>
       </c>
       <c r="I116">
-        <v>0.11021760699986771</v>
+        <v>0.09973776000015278</v>
       </c>
       <c r="J116">
-        <v>0.21714035900004092</v>
+        <v>0.14677485799984424</v>
       </c>
       <c r="K116">
-        <v>3.648160597998867</v>
+        <v>3.2166919649998817</v>
       </c>
       <c r="L116">
-        <v>1263.50390625</v>
+        <v>1269.82421875</v>
       </c>
       <c r="M116">
-        <v>1678.1484375</v>
+        <v>1685.35546875</v>
       </c>
       <c r="N116">
-        <v>1686.875</v>
+        <v>1695.0625</v>
       </c>
       <c r="O116">
         <v>8237.16259765625</v>
@@ -31540,28 +31540,28 @@
         <v>2</v>
       </c>
       <c r="G117">
-        <v>2.671209780999561</v>
+        <v>2.2459688019998794</v>
       </c>
       <c r="H117">
-        <v>0.6822326170004089</v>
+        <v>0.7135851940001885</v>
       </c>
       <c r="I117">
-        <v>0.054548705000343034</v>
+        <v>0.038257295999756025</v>
       </c>
       <c r="J117">
-        <v>0.15996927000014693</v>
+        <v>0.13465033200009202</v>
       </c>
       <c r="K117">
-        <v>3.568447214000116</v>
+        <v>3.1327943030000824</v>
       </c>
       <c r="L117">
-        <v>1625.02734375</v>
+        <v>1632.2265625</v>
       </c>
       <c r="M117">
-        <v>1695.22265625</v>
+        <v>1707.08984375</v>
       </c>
       <c r="N117">
-        <v>1986.90234375</v>
+        <v>2004.1953125</v>
       </c>
       <c r="O117">
         <v>8238.2705078125</v>
@@ -31600,28 +31600,28 @@
         <v>3</v>
       </c>
       <c r="G118">
-        <v>2.594925511999463</v>
+        <v>2.200725779000095</v>
       </c>
       <c r="H118">
-        <v>0.6872621189995698</v>
+        <v>0.4905782190003265</v>
       </c>
       <c r="I118">
-        <v>0.0467414809991169</v>
+        <v>0.04477275399995051</v>
       </c>
       <c r="J118">
-        <v>0.15447452000080375</v>
+        <v>0.14383747600004426</v>
       </c>
       <c r="K118">
-        <v>3.4838336369994067</v>
+        <v>2.8803785439999956</v>
       </c>
       <c r="L118">
-        <v>1642.67578125</v>
+        <v>1649.89453125</v>
       </c>
       <c r="M118">
-        <v>1709.1640625</v>
+        <v>1716.41015625</v>
       </c>
       <c r="N118">
-        <v>1994.42578125</v>
+        <v>2011.77734375</v>
       </c>
       <c r="O118">
         <v>8238.2705078125</v>
@@ -37780,28 +37780,28 @@
         <v>1</v>
       </c>
       <c r="G221">
-        <v>1.0754642120000426</v>
+        <v>0.9546142080002937</v>
       </c>
       <c r="H221">
-        <v>0.8000040209999497</v>
+        <v>0.768623246000061</v>
       </c>
       <c r="I221">
-        <v>0.052163829000164696</v>
+        <v>0.045829979999780335</v>
       </c>
       <c r="J221">
-        <v>0.08316216000002896</v>
+        <v>0.07764049400020667</v>
       </c>
       <c r="K221">
-        <v>2.011256527000114</v>
+        <v>1.8471103329998186</v>
       </c>
       <c r="L221">
-        <v>1263.24609375</v>
+        <v>1270.4140625</v>
       </c>
       <c r="M221">
-        <v>1625.59765625</v>
+        <v>1634.80078125</v>
       </c>
       <c r="N221">
-        <v>1629.30859375</v>
+        <v>1638.61328125</v>
       </c>
       <c r="O221">
         <v>7492.3310546875</v>
@@ -37840,28 +37840,28 @@
         <v>2</v>
       </c>
       <c r="G222">
-        <v>1.3766786769992905</v>
+        <v>1.1542865450001045</v>
       </c>
       <c r="H222">
-        <v>0.5009093979997488</v>
+        <v>0.29522784600021623</v>
       </c>
       <c r="I222">
-        <v>0.02497786499952781</v>
+        <v>0.023531820000243897</v>
       </c>
       <c r="J222">
-        <v>0.07702487400001701</v>
+        <v>0.07283531399980347</v>
       </c>
       <c r="K222">
-        <v>1.9799743599996873</v>
+        <v>1.546279799000331</v>
       </c>
       <c r="L222">
-        <v>1625.59765625</v>
+        <v>1634.80078125</v>
       </c>
       <c r="M222">
-        <v>1636.61328125</v>
+        <v>1646.078125</v>
       </c>
       <c r="N222">
-        <v>1970.875</v>
+        <v>1980.171875</v>
       </c>
       <c r="O222">
         <v>7491.07421875</v>
@@ -37900,28 +37900,28 @@
         <v>3</v>
       </c>
       <c r="G223">
-        <v>1.3078438390002702</v>
+        <v>1.1555849840001429</v>
       </c>
       <c r="H223">
-        <v>0.3022157400000651</v>
+        <v>0.33644842200010316</v>
       </c>
       <c r="I223">
-        <v>0.11020431500037375</v>
+        <v>0.022368996999830415</v>
       </c>
       <c r="J223">
-        <v>0.0728769530005593</v>
+        <v>0.07169309599976259</v>
       </c>
       <c r="K223">
-        <v>1.7935079819999373</v>
+        <v>1.58654995400002</v>
       </c>
       <c r="L223">
-        <v>1636.61328125</v>
+        <v>1646.078125</v>
       </c>
       <c r="M223">
-        <v>1637.41015625</v>
+        <v>1648.4140625</v>
       </c>
       <c r="N223">
-        <v>1980.11328125</v>
+        <v>1989.515625</v>
       </c>
       <c r="O223">
         <v>7491.07421875</v>
@@ -38680,28 +38680,28 @@
         <v>1</v>
       </c>
       <c r="G236">
-        <v>2.1329446460003965</v>
+        <v>2.0334740280000005</v>
       </c>
       <c r="H236">
-        <v>1.1745750850004697</v>
+        <v>1.1493468550002035</v>
       </c>
       <c r="I236">
-        <v>0.12425867799993284</v>
+        <v>0.08916055100007725</v>
       </c>
       <c r="J236">
-        <v>0.2196271679995334</v>
+        <v>0.1515617810000549</v>
       </c>
       <c r="K236">
-        <v>3.6518481220000467</v>
+        <v>3.424120740000035</v>
       </c>
       <c r="L236">
-        <v>1263.09375</v>
+        <v>1270.0625</v>
       </c>
       <c r="M236">
-        <v>1676.84765625</v>
+        <v>1686.50390625</v>
       </c>
       <c r="N236">
-        <v>1686.51171875</v>
+        <v>1695.2890625</v>
       </c>
       <c r="O236">
         <v>8237.16259765625</v>
@@ -38740,28 +38740,28 @@
         <v>2</v>
       </c>
       <c r="G237">
-        <v>2.8444968600006177</v>
+        <v>2.2287902489997578</v>
       </c>
       <c r="H237">
-        <v>0.7581648529994709</v>
+        <v>0.5121837249998862</v>
       </c>
       <c r="I237">
-        <v>0.058149243999650935</v>
+        <v>0.039332020999609085</v>
       </c>
       <c r="J237">
-        <v>0.15988742200079287</v>
+        <v>0.14166901699991286</v>
       </c>
       <c r="K237">
-        <v>3.8211407339995276</v>
+        <v>2.92237920100024</v>
       </c>
       <c r="L237">
-        <v>1622.75390625</v>
+        <v>1633.375</v>
       </c>
       <c r="M237">
-        <v>1698.63671875</v>
+        <v>1703.54296875</v>
       </c>
       <c r="N237">
-        <v>1994.62890625</v>
+        <v>2005.34375</v>
       </c>
       <c r="O237">
         <v>8238.2705078125</v>
@@ -38800,28 +38800,28 @@
         <v>3</v>
       </c>
       <c r="G238">
-        <v>2.7058240480000677</v>
+        <v>2.208074852000209</v>
       </c>
       <c r="H238">
-        <v>0.639344064999932</v>
+        <v>0.6669400360001418</v>
       </c>
       <c r="I238">
-        <v>0.05534724300014204</v>
+        <v>0.04412555499993687</v>
       </c>
       <c r="J238">
-        <v>0.15845751599954383</v>
+        <v>0.13838934799969138</v>
       </c>
       <c r="K238">
-        <v>3.5594197660002465</v>
+        <v>3.057930276999741</v>
       </c>
       <c r="L238">
-        <v>1641.44140625</v>
+        <v>1650.99609375</v>
       </c>
       <c r="M238">
-        <v>1707.8671875</v>
+        <v>1717.96875</v>
       </c>
       <c r="N238">
-        <v>2013.3203125</v>
+        <v>2012.87890625</v>
       </c>
       <c r="O238">
         <v>8238.2705078125</v>
@@ -41380,28 +41380,28 @@
         <v>1</v>
       </c>
       <c r="G281">
-        <v>0.4821823719994427</v>
+        <v>0.6386885040001289</v>
       </c>
       <c r="H281">
-        <v>0.6858818979999342</v>
+        <v>1.4240024959999573</v>
       </c>
       <c r="I281">
-        <v>0.04753156900005706</v>
+        <v>0.05657598900006633</v>
       </c>
       <c r="J281">
-        <v>0.0702024430001984</v>
+        <v>0.08636311300006128</v>
       </c>
       <c r="K281">
-        <v>1.286158740999781</v>
+        <v>2.206190276000143</v>
       </c>
       <c r="L281">
-        <v>1263.03515625</v>
+        <v>1267.90625</v>
       </c>
       <c r="M281">
-        <v>1620.3046875</v>
+        <v>1626.8203125</v>
       </c>
       <c r="N281">
-        <v>1620.3046875</v>
+        <v>1626.8203125</v>
       </c>
       <c r="O281">
         <v>7404.41357421875</v>
@@ -41440,28 +41440,28 @@
         <v>2</v>
       </c>
       <c r="G282">
-        <v>0.8139052559999982</v>
+        <v>0.6448907740000323</v>
       </c>
       <c r="H282">
-        <v>0.30861644499964314</v>
+        <v>0.31655893400011337</v>
       </c>
       <c r="I282">
-        <v>0.024357030999453855</v>
+        <v>0.020963550000033138</v>
       </c>
       <c r="J282">
-        <v>0.08624562499971944</v>
+        <v>0.0667658190000111</v>
       </c>
       <c r="K282">
-        <v>1.2335288760004914</v>
+        <v>1.0496068570000716</v>
       </c>
       <c r="L282">
-        <v>1620.3046875</v>
+        <v>1626.8203125</v>
       </c>
       <c r="M282">
-        <v>1630.22265625</v>
+        <v>1635.90625</v>
       </c>
       <c r="N282">
-        <v>1783.1796875</v>
+        <v>1789.0078125</v>
       </c>
       <c r="O282">
         <v>7412.099609375</v>
@@ -41500,28 +41500,28 @@
         <v>3</v>
       </c>
       <c r="G283">
-        <v>0.7445004020000852</v>
+        <v>0.61447330399983</v>
       </c>
       <c r="H283">
-        <v>0.37045045899958495</v>
+        <v>0.3083011210001132</v>
       </c>
       <c r="I283">
-        <v>0.018257450999954017</v>
+        <v>0.0214336500000627</v>
       </c>
       <c r="J283">
-        <v>0.07052249000025768</v>
+        <v>0.06761589899997489</v>
       </c>
       <c r="K283">
-        <v>1.2041529259995514</v>
+        <v>1.0122489479999786</v>
       </c>
       <c r="L283">
-        <v>1630.22265625</v>
+        <v>1635.90625</v>
       </c>
       <c r="M283">
-        <v>1628.2578125</v>
+        <v>1642.1484375</v>
       </c>
       <c r="N283">
-        <v>1787.22265625</v>
+        <v>1796.3671875</v>
       </c>
       <c r="O283">
         <v>7412.099609375</v>
@@ -46240,28 +46240,28 @@
         <v>1</v>
       </c>
       <c r="G362">
-        <v>0.11907342599999993</v>
+        <v>0.12731721699992704</v>
       </c>
       <c r="H362">
-        <v>1.0815381880000245</v>
+        <v>1.139337926000053</v>
       </c>
       <c r="I362">
-        <v>0.044484061999980895</v>
+        <v>0.03962344599995049</v>
       </c>
       <c r="J362">
-        <v>0.04529757700004211</v>
+        <v>0.0452711249999993</v>
       </c>
       <c r="K362">
-        <v>1.2907030189999773</v>
+        <v>1.3521266019999985</v>
       </c>
       <c r="L362">
-        <v>1260.2890625</v>
+        <v>1267.55078125</v>
       </c>
       <c r="M362">
-        <v>1666.09375</v>
+        <v>1675.02734375</v>
       </c>
       <c r="N362">
-        <v>1666.09375</v>
+        <v>1675.02734375</v>
       </c>
       <c r="O362">
         <v>7194.88330078125</v>
@@ -46300,28 +46300,28 @@
         <v>2</v>
       </c>
       <c r="G363">
-        <v>0.18747748799995634</v>
+        <v>0.14500359399994522</v>
       </c>
       <c r="H363">
-        <v>0.27211605299999064</v>
+        <v>0.3657031380000717</v>
       </c>
       <c r="I363">
-        <v>0.01402968200000032</v>
+        <v>0.012213914999847475</v>
       </c>
       <c r="J363">
-        <v>0.036214778999976716</v>
+        <v>0.036942236999948364</v>
       </c>
       <c r="K363">
-        <v>0.510129027000005</v>
+        <v>0.5602415260000271</v>
       </c>
       <c r="L363">
-        <v>1666.09375</v>
+        <v>1675.02734375</v>
       </c>
       <c r="M363">
-        <v>1671.484375</v>
+        <v>1679.90625</v>
       </c>
       <c r="N363">
-        <v>1744.96875</v>
+        <v>1753.9140625</v>
       </c>
       <c r="O363">
         <v>7197.24072265625</v>
@@ -46360,28 +46360,28 @@
         <v>3</v>
       </c>
       <c r="G364">
-        <v>0.15803509200003418</v>
+        <v>0.14810585999998693</v>
       </c>
       <c r="H364">
-        <v>0.23807987800000774</v>
+        <v>0.25727351399996223</v>
       </c>
       <c r="I364">
-        <v>0.014657782999961455</v>
+        <v>0.014654044999815596</v>
       </c>
       <c r="J364">
-        <v>0.036388001999966946</v>
+        <v>0.03405891500005964</v>
       </c>
       <c r="K364">
-        <v>0.44741061100000934</v>
+        <v>0.454484445999924</v>
       </c>
       <c r="L364">
-        <v>1671.484375</v>
+        <v>1679.90625</v>
       </c>
       <c r="M364">
-        <v>1673.45703125</v>
+        <v>1682.62890625</v>
       </c>
       <c r="N364">
-        <v>1745.109375</v>
+        <v>1758.6015625</v>
       </c>
       <c r="O364">
         <v>7197.24072265625</v>
@@ -57663,12 +57663,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/custom/mural_king/images/scen_3/IMG_8737.jpg</t>
+          <t>/home/kamil/dataset/custom/mural_king/images/scen_3/IMG_8740.jpg</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>IMG_8737.jpg</t>
+          <t>IMG_8740.jpg</t>
         </is>
       </c>
     </row>
@@ -62943,12 +62943,12 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/custom/synagogue/images/scen_2/IMG_8785.jpg</t>
+          <t>/home/kamil/dataset/custom/synagogue/images/scen_2/IMG_8787.jpg</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>IMG_8785.jpg</t>
+          <t>IMG_8787.jpg</t>
         </is>
       </c>
     </row>
@@ -63703,12 +63703,12 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/custom/tennis_table/images/scen_3/IMG_8862.jpg</t>
+          <t>/home/kamil/dataset/custom/tennis_table/images/scen_3/IMG_8861.jpg</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>IMG_8862.jpg</t>
+          <t>IMG_8861.jpg</t>
         </is>
       </c>
     </row>
@@ -65943,12 +65943,12 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/eth3d/exhibition_hall/images/scen_2/DSC_1782.JPG</t>
+          <t>/home/kamil/dataset/eth3d/exhibition_hall/images/scen_2/DSC_1768.JPG</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>DSC_1782.JPG</t>
+          <t>DSC_1768.JPG</t>
         </is>
       </c>
     </row>
@@ -70063,12 +70063,12 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>/home/kamil/dataset/nerf_llff_data/fern/images/scen_1/IMG_4026.JPG</t>
+          <t>/home/kamil/dataset/nerf_llff_data/fern/images/scen_1/IMG_4029.JPG</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>IMG_4026.JPG</t>
+          <t>IMG_4029.JPG</t>
         </is>
       </c>
     </row>
@@ -74866,7 +74866,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10T17:07:57+00:00</t>
+          <t>2026-08-17T10:03:42+00:00</t>
         </is>
       </c>
     </row>
